--- a/rsv_owsa_results.xlsx
+++ b/rsv_owsa_results.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -405,16 +405,16 @@
         <v>0.572</v>
       </c>
       <c r="D2">
-        <v>-79872</v>
+        <v>40904</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>1700616</v>
+        <v>-870917</v>
       </c>
       <c r="G2">
-        <v>1780488</v>
+        <v>911821</v>
       </c>
     </row>
     <row r="3">
@@ -430,122 +430,122 @@
         <v>0.572</v>
       </c>
       <c r="D3">
-        <v>-79779</v>
+        <v>40856</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>1668972</v>
+        <v>-854712</v>
       </c>
       <c r="G3">
-        <v>1748751</v>
+        <v>895568</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>u_disutility_infection</t>
+          <t>o_infected</t>
         </is>
       </c>
       <c r="B4">
-        <v>-0.009599999999999999</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>-0.0115</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>-137752</v>
+        <v>-43313</v>
       </c>
       <c r="E4">
-        <v>-0.007900000000000001</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>-321090</v>
+        <v>256297</v>
       </c>
       <c r="G4">
-        <v>183338</v>
+        <v>299610</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>u_adverse_events</t>
+          <t>u_disutility_infection</t>
         </is>
       </c>
       <c r="B5">
-        <v>-0.12</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="C5">
-        <v>-0.24</v>
+        <v>-0.0115</v>
       </c>
       <c r="D5">
-        <v>-232398</v>
+        <v>70545</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F5">
-        <v>-170862</v>
+        <v>164436</v>
       </c>
       <c r="G5">
-        <v>61536</v>
+        <v>93891</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>o_infected</t>
+          <t>u_adverse_events</t>
         </is>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>-0.12</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>-0.24</v>
       </c>
       <c r="D6">
-        <v>92074</v>
+        <v>119015</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>151007</v>
+        <v>87502</v>
       </c>
       <c r="G6">
-        <v>58934</v>
+        <v>31514</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>c_hfr</t>
+          <t>u_r</t>
         </is>
       </c>
       <c r="B7">
-        <v>92</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="C7">
-        <v>83</v>
+        <v>0.572</v>
       </c>
       <c r="D7">
-        <v>-194111</v>
+        <v>1155</v>
       </c>
       <c r="E7">
-        <v>267</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>-251852</v>
+        <v>-1559</v>
       </c>
       <c r="G7">
-        <v>57741</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>u_r</t>
+          <t>u_v</t>
         </is>
       </c>
       <c r="B8">
@@ -555,41 +555,41 @@
         <v>0.572</v>
       </c>
       <c r="D8">
-        <v>-2256</v>
+        <v>-1109</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8">
-        <v>3044</v>
+        <v>1420</v>
       </c>
       <c r="G8">
-        <v>5300</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>u_v</t>
+          <t>kappa_arexvy</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.8149999999999999</v>
+        <v>0.211</v>
       </c>
       <c r="C9">
-        <v>0.572</v>
+        <v>0.202</v>
       </c>
       <c r="D9">
-        <v>2165</v>
+        <v>99797</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0.22</v>
       </c>
       <c r="F9">
-        <v>-2773</v>
+        <v>101933</v>
       </c>
       <c r="G9">
-        <v>4937</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="10">
@@ -605,16 +605,16 @@
         <v>0.572</v>
       </c>
       <c r="D10">
-        <v>767</v>
+        <v>-393</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10">
-        <v>-999</v>
+        <v>511</v>
       </c>
       <c r="G10">
-        <v>1766</v>
+        <v>904</v>
       </c>
     </row>
     <row r="11">
@@ -630,165 +630,115 @@
         <v>0.572</v>
       </c>
       <c r="D11">
-        <v>-752</v>
+        <v>385</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11">
-        <v>997</v>
+        <v>-511</v>
       </c>
       <c r="G11">
-        <v>1749</v>
+        <v>896</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kappa_arexvy</t>
+          <t>u_disutility_hospitalization</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.211</v>
+        <v>-0.017</v>
       </c>
       <c r="C12">
-        <v>0.202</v>
+        <v>-0.034</v>
       </c>
       <c r="D12">
-        <v>-197581</v>
+        <v>100844</v>
       </c>
       <c r="E12">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>-196275</v>
+        <v>100864</v>
       </c>
       <c r="G12">
-        <v>1306</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>c_death</t>
+          <t>u_h</t>
         </is>
       </c>
       <c r="B13">
-        <v>9067</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="C13">
-        <v>5268</v>
+        <v>0.572</v>
       </c>
       <c r="D13">
-        <v>-197074</v>
+        <v>100851</v>
       </c>
       <c r="E13">
-        <v>12866</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>-196796</v>
+        <v>100856</v>
       </c>
       <c r="G13">
-        <v>278</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>u_disutility_hospitalization</t>
+          <t>kappa_abrysvo</t>
         </is>
       </c>
       <c r="B14">
-        <v>-0.017</v>
+        <v>0.222</v>
       </c>
       <c r="C14">
-        <v>-0.034</v>
+        <v>0.211</v>
       </c>
       <c r="D14">
-        <v>-196916</v>
+        <v>100854</v>
       </c>
       <c r="E14">
+        <v>0.233</v>
+      </c>
+      <c r="F14">
+        <v>100854</v>
+      </c>
+      <c r="G14">
         <v>0</v>
-      </c>
-      <c r="F14">
-        <v>-196954</v>
-      </c>
-      <c r="G14">
-        <v>38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>u_h</t>
+          <t>u_sq</t>
         </is>
       </c>
       <c r="B15">
-        <v>0.8149999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="C15">
-        <v>0.572</v>
+        <v>0.036</v>
       </c>
       <c r="D15">
-        <v>-196929</v>
+        <v>100854</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0.123</v>
       </c>
       <c r="F15">
-        <v>-196939</v>
+        <v>100854</v>
       </c>
       <c r="G15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>kappa_abrysvo</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>0.222</v>
-      </c>
-      <c r="C16">
-        <v>0.211</v>
-      </c>
-      <c r="D16">
-        <v>-196935</v>
-      </c>
-      <c r="E16">
-        <v>0.233</v>
-      </c>
-      <c r="F16">
-        <v>-196935</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>u_sq</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>0.08</v>
-      </c>
-      <c r="C17">
-        <v>0.036</v>
-      </c>
-      <c r="D17">
-        <v>-196935</v>
-      </c>
-      <c r="E17">
-        <v>0.123</v>
-      </c>
-      <c r="F17">
-        <v>-196935</v>
-      </c>
-      <c r="G17">
         <v>0</v>
       </c>
     </row>
@@ -799,7 +749,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -852,16 +802,16 @@
         <v>0.572</v>
       </c>
       <c r="D2">
-        <v>-74167</v>
+        <v>46694</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>1554910</v>
+        <v>-978936</v>
       </c>
       <c r="G2">
-        <v>1629077</v>
+        <v>1025630</v>
       </c>
     </row>
     <row r="3">
@@ -877,66 +827,66 @@
         <v>0.572</v>
       </c>
       <c r="D3">
-        <v>-74080</v>
+        <v>46639</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>1526394</v>
+        <v>-960983</v>
       </c>
       <c r="G3">
-        <v>1600475</v>
+        <v>1007622</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>u_disutility_infection</t>
+          <t>o_infected</t>
         </is>
       </c>
       <c r="B4">
-        <v>-0.009599999999999999</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>-0.0115</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>-127977</v>
+        <v>-49501</v>
       </c>
       <c r="E4">
-        <v>-0.007900000000000001</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>-298785</v>
+        <v>289095</v>
       </c>
       <c r="G4">
-        <v>170808</v>
+        <v>338596</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>o_infected</t>
+          <t>u_disutility_infection</t>
         </is>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>-0.0115</v>
       </c>
       <c r="D5">
-        <v>86017</v>
+        <v>80572</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F5">
-        <v>183803</v>
+        <v>188108</v>
       </c>
       <c r="G5">
-        <v>97787</v>
+        <v>107537</v>
       </c>
     </row>
     <row r="6">
@@ -952,66 +902,66 @@
         <v>-0.24</v>
       </c>
       <c r="D6">
-        <v>-216530</v>
+        <v>136322</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>-158545</v>
+        <v>99816</v>
       </c>
       <c r="G6">
-        <v>57985</v>
+        <v>36506</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>c_hfr</t>
+          <t>u_r</t>
         </is>
       </c>
       <c r="B7">
-        <v>92</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="C7">
-        <v>83</v>
+        <v>0.572</v>
       </c>
       <c r="D7">
-        <v>-180226</v>
+        <v>1318</v>
       </c>
       <c r="E7">
-        <v>267</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>-238067</v>
+        <v>-1778</v>
       </c>
       <c r="G7">
-        <v>57841</v>
+        <v>3096</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>u_r</t>
+          <t>kappa_abrysvo</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.8149999999999999</v>
+        <v>0.222</v>
       </c>
       <c r="C8">
-        <v>0.572</v>
+        <v>0.211</v>
       </c>
       <c r="D8">
-        <v>-2093</v>
+        <v>113756</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0.233</v>
       </c>
       <c r="F8">
-        <v>2824</v>
+        <v>116779</v>
       </c>
       <c r="G8">
-        <v>4918</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="9">
@@ -1027,47 +977,47 @@
         <v>0.572</v>
       </c>
       <c r="D9">
-        <v>2008</v>
+        <v>-1264</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9">
-        <v>-2573</v>
+        <v>1620</v>
       </c>
       <c r="G9">
-        <v>4581</v>
+        <v>2884</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kappa_abrysvo</t>
+          <t>u_s_ve</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.222</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="C10">
-        <v>0.211</v>
+        <v>0.572</v>
       </c>
       <c r="D10">
-        <v>-184033</v>
+        <v>-444</v>
       </c>
       <c r="E10">
-        <v>0.233</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>-182052</v>
+        <v>578</v>
       </c>
       <c r="G10">
-        <v>1982</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>u_s_ve</t>
+          <t>u_s_vn</t>
         </is>
       </c>
       <c r="B11">
@@ -1077,165 +1027,115 @@
         <v>0.572</v>
       </c>
       <c r="D11">
-        <v>705</v>
+        <v>435</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11">
-        <v>-918</v>
+        <v>-577</v>
       </c>
       <c r="G11">
-        <v>1623</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>u_s_vn</t>
+          <t>u_disutility_hospitalization</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.8149999999999999</v>
+        <v>-0.017</v>
       </c>
       <c r="C12">
-        <v>0.572</v>
+        <v>-0.034</v>
       </c>
       <c r="D12">
-        <v>-692</v>
+        <v>115236</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>917</v>
+        <v>115259</v>
       </c>
       <c r="G12">
-        <v>1608</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>c_death</t>
+          <t>u_h</t>
         </is>
       </c>
       <c r="B13">
-        <v>9067</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="C13">
-        <v>5268</v>
+        <v>0.572</v>
       </c>
       <c r="D13">
-        <v>-183195</v>
+        <v>115244</v>
       </c>
       <c r="E13">
-        <v>12866</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>-182916</v>
+        <v>115250</v>
       </c>
       <c r="G13">
-        <v>279</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>u_disutility_hospitalization</t>
+          <t>kappa_arexvy</t>
         </is>
       </c>
       <c r="B14">
-        <v>-0.017</v>
+        <v>0.211</v>
       </c>
       <c r="C14">
-        <v>-0.034</v>
+        <v>0.202</v>
       </c>
       <c r="D14">
-        <v>-183037</v>
+        <v>115247</v>
       </c>
       <c r="E14">
+        <v>0.22</v>
+      </c>
+      <c r="F14">
+        <v>115247</v>
+      </c>
+      <c r="G14">
         <v>0</v>
-      </c>
-      <c r="F14">
-        <v>-183073</v>
-      </c>
-      <c r="G14">
-        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>u_h</t>
+          <t>u_sq</t>
         </is>
       </c>
       <c r="B15">
-        <v>0.8149999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="C15">
-        <v>0.572</v>
+        <v>0.036</v>
       </c>
       <c r="D15">
-        <v>-183050</v>
+        <v>115247</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0.123</v>
       </c>
       <c r="F15">
-        <v>-183059</v>
+        <v>115248</v>
       </c>
       <c r="G15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>kappa_arexvy</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>0.211</v>
-      </c>
-      <c r="C16">
-        <v>0.202</v>
-      </c>
-      <c r="D16">
-        <v>-183055</v>
-      </c>
-      <c r="E16">
-        <v>0.22</v>
-      </c>
-      <c r="F16">
-        <v>-183055</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>u_sq</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>0.08</v>
-      </c>
-      <c r="C17">
-        <v>0.036</v>
-      </c>
-      <c r="D17">
-        <v>-183055</v>
-      </c>
-      <c r="E17">
-        <v>0.123</v>
-      </c>
-      <c r="F17">
-        <v>-183055</v>
-      </c>
-      <c r="G17">
         <v>0</v>
       </c>
     </row>

--- a/rsv_owsa_results.xlsx
+++ b/rsv_owsa_results.xlsx
@@ -7,8 +7,10 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Arexvy OWSA" sheetId="1" r:id="rId1"/>
-    <sheet name="Abrysvo OWSA" sheetId="2" r:id="rId2"/>
+    <sheet name="AREXVY 100K WTP" sheetId="1" r:id="rId1"/>
+    <sheet name="AREXVY 150K WTP" sheetId="2" r:id="rId2"/>
+    <sheet name="ABRYSVO 100K WTP" sheetId="3" r:id="rId3"/>
+    <sheet name="ABRYSVO 150K WTP" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -352,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -373,7 +375,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ICER at Lower</t>
+          <t>INMB at Lower</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -383,19 +385,19 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ICER at Upper</t>
+          <t>INMB at Upper</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ICER Range</t>
+          <t>INMB Range</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>u_i</t>
+          <t>u_s_vn</t>
         </is>
       </c>
       <c r="B2">
@@ -405,22 +407,22 @@
         <v>0.572</v>
       </c>
       <c r="D2">
-        <v>40904</v>
+        <v>4973938103784</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>-870917</v>
+        <v>-3688111710561</v>
       </c>
       <c r="G2">
-        <v>911821</v>
+        <v>8662049814345</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>u_e</t>
+          <t>u_s_ve</t>
         </is>
       </c>
       <c r="B3">
@@ -430,97 +432,97 @@
         <v>0.572</v>
       </c>
       <c r="D3">
-        <v>40856</v>
+        <v>-4804511703751</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>-854712</v>
+        <v>3756387114107</v>
       </c>
       <c r="G3">
-        <v>895568</v>
+        <v>8560898817858</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>o_infected</t>
+          <t>u_v</t>
         </is>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>0.572</v>
       </c>
       <c r="D4">
-        <v>-43313</v>
+        <v>-1678603242561</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>256297</v>
+        <v>1376580260937</v>
       </c>
       <c r="G4">
-        <v>299610</v>
+        <v>3055183503499</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>u_disutility_infection</t>
+          <t>u_r</t>
         </is>
       </c>
       <c r="B5">
-        <v>-0.009599999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="C5">
-        <v>-0.0115</v>
+        <v>0.572</v>
       </c>
       <c r="D5">
-        <v>70545</v>
+        <v>1683434810681</v>
       </c>
       <c r="E5">
-        <v>-0.007900000000000001</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>164436</v>
+        <v>-1182996034741</v>
       </c>
       <c r="G5">
-        <v>93891</v>
+        <v>2866430845422</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>u_adverse_events</t>
+          <t>u_e</t>
         </is>
       </c>
       <c r="B6">
-        <v>-0.12</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="C6">
-        <v>-0.24</v>
+        <v>0.572</v>
       </c>
       <c r="D6">
-        <v>119015</v>
+        <v>83693030269</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>87502</v>
+        <v>34914374215</v>
       </c>
       <c r="G6">
-        <v>31514</v>
+        <v>48778656054</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>u_r</t>
+          <t>u_i</t>
         </is>
       </c>
       <c r="B7">
@@ -530,215 +532,465 @@
         <v>0.572</v>
       </c>
       <c r="D7">
-        <v>1155</v>
+        <v>83638642279</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>-1559</v>
+        <v>34955780710</v>
       </c>
       <c r="G7">
-        <v>2714</v>
+        <v>48682861569</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>u_v</t>
+          <t>u_disutility_infection</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.8149999999999999</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="C8">
-        <v>0.572</v>
+        <v>-0.0115</v>
       </c>
       <c r="D8">
-        <v>-1109</v>
+        <v>64100989284</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F8">
-        <v>1420</v>
+        <v>48706462626</v>
       </c>
       <c r="G8">
-        <v>2529</v>
+        <v>15394526659</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kappa_arexvy</t>
+          <t>c_hfr</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.211</v>
+        <v>92</v>
       </c>
       <c r="C9">
-        <v>0.202</v>
+        <v>83</v>
       </c>
       <c r="D9">
-        <v>99797</v>
+        <v>55465972659</v>
       </c>
       <c r="E9">
-        <v>0.22</v>
+        <v>267</v>
       </c>
       <c r="F9">
-        <v>101933</v>
+        <v>66355373335</v>
       </c>
       <c r="G9">
-        <v>2136</v>
+        <v>10889400675</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>u_s_ve</t>
+          <t>c_arexvy</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.8149999999999999</v>
+        <v>280</v>
       </c>
       <c r="C10">
-        <v>0.572</v>
+        <v>224</v>
       </c>
       <c r="D10">
-        <v>-393</v>
+        <v>59492346909</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>336</v>
       </c>
       <c r="F10">
-        <v>511</v>
+        <v>52504865867</v>
       </c>
       <c r="G10">
-        <v>904</v>
+        <v>6987481042</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>u_s_vn</t>
+          <t>u_adverse_events</t>
         </is>
       </c>
       <c r="B11">
-        <v>0.8149999999999999</v>
+        <v>-0.12</v>
       </c>
       <c r="C11">
-        <v>0.572</v>
+        <v>-0.24</v>
       </c>
       <c r="D11">
-        <v>385</v>
+        <v>53120810182</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>-511</v>
+        <v>58876402594</v>
       </c>
       <c r="G11">
-        <v>896</v>
+        <v>5755592412</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>u_disutility_hospitalization</t>
+          <t>c_vac_admin</t>
         </is>
       </c>
       <c r="B12">
-        <v>-0.017</v>
+        <v>25</v>
       </c>
       <c r="C12">
-        <v>-0.034</v>
+        <v>19</v>
       </c>
       <c r="D12">
-        <v>100844</v>
+        <v>56372935730</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F12">
-        <v>100864</v>
+        <v>55499500599</v>
       </c>
       <c r="G12">
-        <v>20</v>
+        <v>873435130</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>u_h</t>
+          <t>o_infected</t>
         </is>
       </c>
       <c r="B13">
-        <v>0.8149999999999999</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>0.572</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>100851</v>
+        <v>-1999903468</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F13">
-        <v>100856</v>
+        <v>-2592403851</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>592500383</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kappa_abrysvo</t>
+          <t>c_death</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.222</v>
+        <v>9067</v>
       </c>
       <c r="C14">
-        <v>0.211</v>
+        <v>5268</v>
       </c>
       <c r="D14">
-        <v>100854</v>
+        <v>56024864784</v>
       </c>
       <c r="E14">
-        <v>0.233</v>
+        <v>12866</v>
       </c>
       <c r="F14">
-        <v>100854</v>
+        <v>55972347993</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>52516791</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>u_disutility_hospitalization</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>-0.017</v>
+      </c>
+      <c r="C15">
+        <v>-0.034</v>
+      </c>
+      <c r="D15">
+        <v>56000435551</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>55996777225</v>
+      </c>
+      <c r="G15">
+        <v>3658326</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>u_h</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="C16">
+        <v>0.572</v>
+      </c>
+      <c r="D16">
+        <v>55999174081</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>55998174195</v>
+      </c>
+      <c r="G16">
+        <v>999886</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>u_sq</t>
         </is>
       </c>
-      <c r="B15">
+      <c r="B17">
         <v>0.08</v>
       </c>
-      <c r="C15">
+      <c r="C17">
         <v>0.036</v>
       </c>
-      <c r="D15">
-        <v>100854</v>
-      </c>
-      <c r="E15">
+      <c r="D17">
+        <v>55998622375</v>
+      </c>
+      <c r="E17">
         <v>0.123</v>
       </c>
-      <c r="F15">
-        <v>100854</v>
-      </c>
-      <c r="G15">
+      <c r="F17">
+        <v>55998590764</v>
+      </c>
+      <c r="G17">
+        <v>31611</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>i_0_p</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>0.0003</v>
+      </c>
+      <c r="C18">
+        <v>0.0002</v>
+      </c>
+      <c r="D18">
+        <v>55998606388</v>
+      </c>
+      <c r="E18">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="F18">
+        <v>55998606388</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>h_0_p</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>55998606388</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>55998606388</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>phi</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>55998606388</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>55998606388</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>rho</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>0.18</v>
+      </c>
+      <c r="C21">
+        <v>0.089</v>
+      </c>
+      <c r="D21">
+        <v>55998606388</v>
+      </c>
+      <c r="E21">
+        <v>0.327</v>
+      </c>
+      <c r="F21">
+        <v>55998606388</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>delta_s</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>0.0713</v>
+      </c>
+      <c r="C22">
+        <v>0.054</v>
+      </c>
+      <c r="D22">
+        <v>55998606388</v>
+      </c>
+      <c r="E22">
+        <v>0.0936</v>
+      </c>
+      <c r="F22">
+        <v>55998606388</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>p_adverse_events</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>0.2</v>
+      </c>
+      <c r="C23">
+        <v>0.16</v>
+      </c>
+      <c r="D23">
+        <v>55998606388</v>
+      </c>
+      <c r="E23">
+        <v>0.25</v>
+      </c>
+      <c r="F23">
+        <v>55998606388</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>c_abrysvo</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>319</v>
+      </c>
+      <c r="C24">
+        <v>255.2</v>
+      </c>
+      <c r="D24">
+        <v>55998606388</v>
+      </c>
+      <c r="E24">
+        <v>382.8</v>
+      </c>
+      <c r="F24">
+        <v>55998606388</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>o_los_h</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>6.2</v>
+      </c>
+      <c r="C25">
+        <v>1.2258</v>
+      </c>
+      <c r="D25">
+        <v>55998606388</v>
+      </c>
+      <c r="E25">
+        <v>5.0582</v>
+      </c>
+      <c r="F25">
+        <v>55998606388</v>
+      </c>
+      <c r="G25">
         <v>0</v>
       </c>
     </row>
@@ -749,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -770,7 +1022,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ICER at Lower</t>
+          <t>INMB at Lower</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -780,19 +1032,19 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ICER at Upper</t>
+          <t>INMB at Upper</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ICER Range</t>
+          <t>INMB Range</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>u_i</t>
+          <t>u_s_vn</t>
         </is>
       </c>
       <c r="B2">
@@ -802,22 +1054,22 @@
         <v>0.572</v>
       </c>
       <c r="D2">
-        <v>46694</v>
+        <v>7442337265212</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>-978936</v>
+        <v>-5550737456305</v>
       </c>
       <c r="G2">
-        <v>1025630</v>
+        <v>12993074721517</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>u_e</t>
+          <t>u_s_ve</t>
         </is>
       </c>
       <c r="B3">
@@ -827,97 +1079,97 @@
         <v>0.572</v>
       </c>
       <c r="D3">
-        <v>46639</v>
+        <v>-7225337446089</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>-960983</v>
+        <v>5616010780698</v>
       </c>
       <c r="G3">
-        <v>1007622</v>
+        <v>12841348226787</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>o_infected</t>
+          <t>u_v</t>
         </is>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>0.572</v>
       </c>
       <c r="D4">
-        <v>-49501</v>
+        <v>-2536474754305</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>289095</v>
+        <v>2046300500943</v>
       </c>
       <c r="G4">
-        <v>338596</v>
+        <v>4582775255248</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>u_disutility_infection</t>
+          <t>u_r</t>
         </is>
       </c>
       <c r="B5">
-        <v>-0.009599999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="C5">
-        <v>-0.0115</v>
+        <v>0.572</v>
       </c>
       <c r="D5">
-        <v>80572</v>
+        <v>2506582325559</v>
       </c>
       <c r="E5">
-        <v>-0.007900000000000001</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>188108</v>
+        <v>-1793063942575</v>
       </c>
       <c r="G5">
-        <v>107537</v>
+        <v>4299646268133</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>u_adverse_events</t>
+          <t>u_e</t>
         </is>
       </c>
       <c r="B6">
-        <v>-0.12</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="C6">
-        <v>-0.24</v>
+        <v>0.572</v>
       </c>
       <c r="D6">
-        <v>136322</v>
+        <v>106969654941</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>99816</v>
+        <v>33801670859</v>
       </c>
       <c r="G6">
-        <v>36506</v>
+        <v>73167984081</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>u_r</t>
+          <t>u_i</t>
         </is>
       </c>
       <c r="B7">
@@ -927,215 +1179,1759 @@
         <v>0.572</v>
       </c>
       <c r="D7">
-        <v>1318</v>
+        <v>106888072955</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>-1778</v>
+        <v>33863780601</v>
       </c>
       <c r="G7">
-        <v>3096</v>
+        <v>73024292354</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kappa_abrysvo</t>
+          <t>u_disutility_infection</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.222</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="C8">
-        <v>0.211</v>
+        <v>-0.0115</v>
       </c>
       <c r="D8">
-        <v>113756</v>
+        <v>77581593463</v>
       </c>
       <c r="E8">
-        <v>0.233</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F8">
-        <v>116779</v>
+        <v>54489803475</v>
       </c>
       <c r="G8">
-        <v>3023</v>
+        <v>23091789988</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>u_v</t>
+          <t>o_infected</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.8149999999999999</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>0.572</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>-1264</v>
+        <v>-14615181566</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F9">
-        <v>1620</v>
+        <v>-51150149</v>
       </c>
       <c r="G9">
-        <v>2884</v>
+        <v>14564031416</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>u_s_ve</t>
+          <t>c_hfr</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.8149999999999999</v>
+        <v>92</v>
       </c>
       <c r="C10">
-        <v>0.572</v>
+        <v>83</v>
       </c>
       <c r="D10">
-        <v>-444</v>
+        <v>64895385390</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>267</v>
       </c>
       <c r="F10">
-        <v>578</v>
+        <v>75784786065</v>
       </c>
       <c r="G10">
-        <v>1022</v>
+        <v>10889400675</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>u_s_vn</t>
+          <t>u_adverse_events</t>
         </is>
       </c>
       <c r="B11">
-        <v>0.8149999999999999</v>
+        <v>-0.12</v>
       </c>
       <c r="C11">
-        <v>0.572</v>
+        <v>-0.24</v>
       </c>
       <c r="D11">
-        <v>435</v>
+        <v>61111324809</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>-577</v>
+        <v>69744713428</v>
       </c>
       <c r="G11">
-        <v>1013</v>
+        <v>8633388619</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>u_disutility_hospitalization</t>
+          <t>c_arexvy</t>
         </is>
       </c>
       <c r="B12">
-        <v>-0.017</v>
+        <v>280</v>
       </c>
       <c r="C12">
-        <v>-0.034</v>
+        <v>224</v>
       </c>
       <c r="D12">
-        <v>115236</v>
+        <v>68921759640</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="F12">
-        <v>115259</v>
+        <v>61934278598</v>
       </c>
       <c r="G12">
-        <v>22</v>
+        <v>6987481042</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>u_h</t>
+          <t>c_vac_admin</t>
         </is>
       </c>
       <c r="B13">
-        <v>0.8149999999999999</v>
+        <v>25</v>
       </c>
       <c r="C13">
-        <v>0.572</v>
+        <v>19</v>
       </c>
       <c r="D13">
-        <v>115244</v>
+        <v>65802348460</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="F13">
-        <v>115250</v>
+        <v>64928913330</v>
       </c>
       <c r="G13">
-        <v>6</v>
+        <v>873435130</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kappa_arexvy</t>
+          <t>c_death</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.211</v>
+        <v>9067</v>
       </c>
       <c r="C14">
-        <v>0.202</v>
+        <v>5268</v>
       </c>
       <c r="D14">
-        <v>115247</v>
+        <v>65454277514</v>
       </c>
       <c r="E14">
-        <v>0.22</v>
+        <v>12866</v>
       </c>
       <c r="F14">
-        <v>115247</v>
+        <v>65401760723</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>52516791</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>u_disutility_hospitalization</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>-0.017</v>
+      </c>
+      <c r="C15">
+        <v>-0.034</v>
+      </c>
+      <c r="D15">
+        <v>65430762863</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>65425275375</v>
+      </c>
+      <c r="G15">
+        <v>5487488</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>u_h</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="C16">
+        <v>0.572</v>
+      </c>
+      <c r="D16">
+        <v>65428870658</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>65427370829</v>
+      </c>
+      <c r="G16">
+        <v>1499829</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>u_sq</t>
         </is>
       </c>
+      <c r="B17">
+        <v>0.08</v>
+      </c>
+      <c r="C17">
+        <v>0.036</v>
+      </c>
+      <c r="D17">
+        <v>65428043099</v>
+      </c>
+      <c r="E17">
+        <v>0.123</v>
+      </c>
+      <c r="F17">
+        <v>65427995683</v>
+      </c>
+      <c r="G17">
+        <v>47416</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>i_0_p</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>0.0003</v>
+      </c>
+      <c r="C18">
+        <v>0.0002</v>
+      </c>
+      <c r="D18">
+        <v>65428019119</v>
+      </c>
+      <c r="E18">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="F18">
+        <v>65428019119</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>h_0_p</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>65428019119</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>65428019119</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>phi</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>65428019119</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>65428019119</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>rho</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>0.18</v>
+      </c>
+      <c r="C21">
+        <v>0.089</v>
+      </c>
+      <c r="D21">
+        <v>65428019119</v>
+      </c>
+      <c r="E21">
+        <v>0.327</v>
+      </c>
+      <c r="F21">
+        <v>65428019119</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>delta_s</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>0.0713</v>
+      </c>
+      <c r="C22">
+        <v>0.054</v>
+      </c>
+      <c r="D22">
+        <v>65428019119</v>
+      </c>
+      <c r="E22">
+        <v>0.0936</v>
+      </c>
+      <c r="F22">
+        <v>65428019119</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>p_adverse_events</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>0.2</v>
+      </c>
+      <c r="C23">
+        <v>0.16</v>
+      </c>
+      <c r="D23">
+        <v>65428019119</v>
+      </c>
+      <c r="E23">
+        <v>0.25</v>
+      </c>
+      <c r="F23">
+        <v>65428019119</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>c_abrysvo</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>319</v>
+      </c>
+      <c r="C24">
+        <v>255.2</v>
+      </c>
+      <c r="D24">
+        <v>65428019119</v>
+      </c>
+      <c r="E24">
+        <v>382.8</v>
+      </c>
+      <c r="F24">
+        <v>65428019119</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>o_los_h</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>6.2</v>
+      </c>
+      <c r="C25">
+        <v>1.2258</v>
+      </c>
+      <c r="D25">
+        <v>65428019119</v>
+      </c>
+      <c r="E25">
+        <v>5.0582</v>
+      </c>
+      <c r="F25">
+        <v>65428019119</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Base Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Lower Bound</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>INMB at Lower</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Upper Bound</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>INMB at Upper</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>INMB Range</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>u_s_vn</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="C2">
+        <v>0.572</v>
+      </c>
+      <c r="D2">
+        <v>4963999682670</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>-3686305242446</v>
+      </c>
+      <c r="G2">
+        <v>8650304925115</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>u_s_ve</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="C3">
+        <v>0.572</v>
+      </c>
+      <c r="D3">
+        <v>-4801457784637</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>3748302294394</v>
+      </c>
+      <c r="G3">
+        <v>8549760079032</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>u_v</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="C4">
+        <v>0.572</v>
+      </c>
+      <c r="D4">
+        <v>-1663882518416</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1359613305707</v>
+      </c>
+      <c r="G4">
+        <v>3023495824123</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>u_r</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="C5">
+        <v>0.572</v>
+      </c>
+      <c r="D5">
+        <v>1663041127972</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>-1173229799567</v>
+      </c>
+      <c r="G5">
+        <v>2836270927539</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>u_e</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="C6">
+        <v>0.572</v>
+      </c>
+      <c r="D6">
+        <v>80131458059</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>31866039666</v>
+      </c>
+      <c r="G6">
+        <v>48265418393</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>u_i</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="C7">
+        <v>0.572</v>
+      </c>
+      <c r="D7">
+        <v>80077642327</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>31907010490</v>
+      </c>
+      <c r="G7">
+        <v>48170631837</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>u_disutility_infection</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="C8">
+        <v>-0.0115</v>
+      </c>
+      <c r="D8">
+        <v>60745559968</v>
+      </c>
+      <c r="E8">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F8">
+        <v>45513010934</v>
+      </c>
+      <c r="G8">
+        <v>15232549034</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>c_hfr</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>92</v>
+      </c>
+      <c r="C9">
+        <v>83</v>
+      </c>
+      <c r="D9">
+        <v>52201398977</v>
+      </c>
+      <c r="E9">
+        <v>267</v>
+      </c>
+      <c r="F9">
+        <v>62976223914</v>
+      </c>
+      <c r="G9">
+        <v>10774824937</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>c_abrysvo</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>319</v>
+      </c>
+      <c r="C10">
+        <v>255.2</v>
+      </c>
+      <c r="D10">
+        <v>56711668364</v>
+      </c>
+      <c r="E10">
+        <v>382.8</v>
+      </c>
+      <c r="F10">
+        <v>48745188551</v>
+      </c>
+      <c r="G10">
+        <v>7966479813</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>u_adverse_events</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>-0.12</v>
+      </c>
+      <c r="C11">
+        <v>-0.24</v>
+      </c>
+      <c r="D11">
+        <v>49848556352</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>55608300565</v>
+      </c>
+      <c r="G11">
+        <v>5759744212</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>c_vac_admin</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>25</v>
+      </c>
+      <c r="C12">
+        <v>19</v>
+      </c>
+      <c r="D12">
+        <v>53103027821</v>
+      </c>
+      <c r="E12">
+        <v>33</v>
+      </c>
+      <c r="F12">
+        <v>52228962638</v>
+      </c>
+      <c r="G12">
+        <v>874065183</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>o_infected</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>-3481364948</v>
+      </c>
+      <c r="E13">
+        <v>8</v>
+      </c>
+      <c r="F13">
+        <v>-4258925693</v>
+      </c>
+      <c r="G13">
+        <v>777560744</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>c_death</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>9067</v>
+      </c>
+      <c r="C14">
+        <v>5268</v>
+      </c>
+      <c r="D14">
+        <v>52754410266</v>
+      </c>
+      <c r="E14">
+        <v>12866</v>
+      </c>
+      <c r="F14">
+        <v>52702446648</v>
+      </c>
+      <c r="G14">
+        <v>51963618</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>u_disutility_hospitalization</t>
+        </is>
+      </c>
       <c r="B15">
+        <v>-0.017</v>
+      </c>
+      <c r="C15">
+        <v>-0.034</v>
+      </c>
+      <c r="D15">
+        <v>52730238374</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>52726618541</v>
+      </c>
+      <c r="G15">
+        <v>3619834</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>u_h</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="C16">
+        <v>0.572</v>
+      </c>
+      <c r="D16">
+        <v>52728990176</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>52728000811</v>
+      </c>
+      <c r="G16">
+        <v>989365</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>u_sq</t>
+        </is>
+      </c>
+      <c r="B17">
         <v>0.08</v>
       </c>
+      <c r="C17">
+        <v>0.036</v>
+      </c>
+      <c r="D17">
+        <v>52728444276</v>
+      </c>
+      <c r="E17">
+        <v>0.123</v>
+      </c>
+      <c r="F17">
+        <v>52728412998</v>
+      </c>
+      <c r="G17">
+        <v>31278</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>i_0_p</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>0.0003</v>
+      </c>
+      <c r="C18">
+        <v>0.0002</v>
+      </c>
+      <c r="D18">
+        <v>52728428457</v>
+      </c>
+      <c r="E18">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="F18">
+        <v>52728428457</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>h_0_p</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>52728428457</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>52728428457</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>phi</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>52728428457</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>52728428457</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>rho</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>0.18</v>
+      </c>
+      <c r="C21">
+        <v>0.089</v>
+      </c>
+      <c r="D21">
+        <v>52728428457</v>
+      </c>
+      <c r="E21">
+        <v>0.327</v>
+      </c>
+      <c r="F21">
+        <v>52728428457</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>delta_s</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>0.0713</v>
+      </c>
+      <c r="C22">
+        <v>0.054</v>
+      </c>
+      <c r="D22">
+        <v>52728428457</v>
+      </c>
+      <c r="E22">
+        <v>0.0936</v>
+      </c>
+      <c r="F22">
+        <v>52728428457</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>p_adverse_events</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>0.2</v>
+      </c>
+      <c r="C23">
+        <v>0.16</v>
+      </c>
+      <c r="D23">
+        <v>52728428457</v>
+      </c>
+      <c r="E23">
+        <v>0.25</v>
+      </c>
+      <c r="F23">
+        <v>52728428457</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>c_arexvy</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>280</v>
+      </c>
+      <c r="C24">
+        <v>224</v>
+      </c>
+      <c r="D24">
+        <v>52728428457</v>
+      </c>
+      <c r="E24">
+        <v>336</v>
+      </c>
+      <c r="F24">
+        <v>52728428457</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>o_los_h</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>6.2</v>
+      </c>
+      <c r="C25">
+        <v>1.2258</v>
+      </c>
+      <c r="D25">
+        <v>52728428457</v>
+      </c>
+      <c r="E25">
+        <v>5.0582</v>
+      </c>
+      <c r="F25">
+        <v>52728428457</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Base Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Lower Bound</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>INMB at Lower</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Upper Bound</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>INMB at Upper</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>INMB Range</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>u_s_vn</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="C2">
+        <v>0.572</v>
+      </c>
+      <c r="D2">
+        <v>7428949438495</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>-5546507949178</v>
+      </c>
+      <c r="G2">
+        <v>12975457387673</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>u_s_ve</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="C3">
+        <v>0.572</v>
+      </c>
+      <c r="D3">
+        <v>-7219236762466</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>5605403356082</v>
+      </c>
+      <c r="G3">
+        <v>12824640118547</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>u_v</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="C4">
+        <v>0.572</v>
+      </c>
+      <c r="D4">
+        <v>-2512873863133</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2022369873051</v>
+      </c>
+      <c r="G4">
+        <v>4535243736184</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>u_r</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="C5">
+        <v>0.572</v>
+      </c>
+      <c r="D5">
+        <v>2477511606449</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>-1776894784860</v>
+      </c>
+      <c r="G5">
+        <v>4254406391309</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>u_e</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="C6">
+        <v>0.572</v>
+      </c>
+      <c r="D6">
+        <v>103147101579</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>30748973990</v>
+      </c>
+      <c r="G6">
+        <v>72398127589</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>u_i</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="C7">
+        <v>0.572</v>
+      </c>
+      <c r="D7">
+        <v>103066377981</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>30810430226</v>
+      </c>
+      <c r="G7">
+        <v>72255947755</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>u_disutility_infection</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="C8">
+        <v>-0.0115</v>
+      </c>
+      <c r="D8">
+        <v>74068254443</v>
+      </c>
+      <c r="E8">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F8">
+        <v>51219430892</v>
+      </c>
+      <c r="G8">
+        <v>22848823551</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>o_infected</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>-15929491849</v>
+      </c>
+      <c r="E9">
+        <v>8</v>
+      </c>
+      <c r="F9">
+        <v>-1717869478</v>
+      </c>
+      <c r="G9">
+        <v>14211622371</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>c_hfr</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>92</v>
+      </c>
+      <c r="C10">
+        <v>83</v>
+      </c>
+      <c r="D10">
+        <v>61515527696</v>
+      </c>
+      <c r="E10">
+        <v>267</v>
+      </c>
+      <c r="F10">
+        <v>72290352633</v>
+      </c>
+      <c r="G10">
+        <v>10774824937</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>u_adverse_events</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>-0.12</v>
+      </c>
+      <c r="C11">
+        <v>-0.24</v>
+      </c>
+      <c r="D11">
+        <v>57722749019</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>66362365337</v>
+      </c>
+      <c r="G11">
+        <v>8639616318</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>c_abrysvo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>319</v>
+      </c>
+      <c r="C12">
+        <v>255.2</v>
+      </c>
+      <c r="D12">
+        <v>66025797083</v>
+      </c>
+      <c r="E12">
+        <v>382.8</v>
+      </c>
+      <c r="F12">
+        <v>58059317270</v>
+      </c>
+      <c r="G12">
+        <v>7966479813</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>c_vac_admin</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>25</v>
+      </c>
+      <c r="C13">
+        <v>19</v>
+      </c>
+      <c r="D13">
+        <v>62417156541</v>
+      </c>
+      <c r="E13">
+        <v>33</v>
+      </c>
+      <c r="F13">
+        <v>61543091357</v>
+      </c>
+      <c r="G13">
+        <v>874065183</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>c_death</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>9067</v>
+      </c>
+      <c r="C14">
+        <v>5268</v>
+      </c>
+      <c r="D14">
+        <v>62068538986</v>
+      </c>
+      <c r="E14">
+        <v>12866</v>
+      </c>
+      <c r="F14">
+        <v>62016575367</v>
+      </c>
+      <c r="G14">
+        <v>51963618</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>u_disutility_hospitalization</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>-0.017</v>
+      </c>
       <c r="C15">
+        <v>-0.034</v>
+      </c>
+      <c r="D15">
+        <v>62045272052</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>62039842302</v>
+      </c>
+      <c r="G15">
+        <v>5429750</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>u_h</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="C16">
+        <v>0.572</v>
+      </c>
+      <c r="D16">
+        <v>62043399755</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>62041915707</v>
+      </c>
+      <c r="G16">
+        <v>1484048</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>u_sq</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>0.08</v>
+      </c>
+      <c r="C17">
         <v>0.036</v>
       </c>
-      <c r="D15">
-        <v>115247</v>
-      </c>
-      <c r="E15">
+      <c r="D17">
+        <v>62042580904</v>
+      </c>
+      <c r="E17">
         <v>0.123</v>
       </c>
-      <c r="F15">
-        <v>115248</v>
-      </c>
-      <c r="G15">
+      <c r="F17">
+        <v>62042533987</v>
+      </c>
+      <c r="G17">
+        <v>46917</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>i_0_p</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>0.0003</v>
+      </c>
+      <c r="C18">
+        <v>0.0002</v>
+      </c>
+      <c r="D18">
+        <v>62042557176</v>
+      </c>
+      <c r="E18">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="F18">
+        <v>62042557176</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>h_0_p</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>62042557176</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>62042557176</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>phi</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>62042557176</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>62042557176</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>rho</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>0.18</v>
+      </c>
+      <c r="C21">
+        <v>0.089</v>
+      </c>
+      <c r="D21">
+        <v>62042557176</v>
+      </c>
+      <c r="E21">
+        <v>0.327</v>
+      </c>
+      <c r="F21">
+        <v>62042557176</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>delta_s</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>0.0713</v>
+      </c>
+      <c r="C22">
+        <v>0.054</v>
+      </c>
+      <c r="D22">
+        <v>62042557176</v>
+      </c>
+      <c r="E22">
+        <v>0.0936</v>
+      </c>
+      <c r="F22">
+        <v>62042557176</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>p_adverse_events</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>0.2</v>
+      </c>
+      <c r="C23">
+        <v>0.16</v>
+      </c>
+      <c r="D23">
+        <v>62042557176</v>
+      </c>
+      <c r="E23">
+        <v>0.25</v>
+      </c>
+      <c r="F23">
+        <v>62042557176</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>c_arexvy</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>280</v>
+      </c>
+      <c r="C24">
+        <v>224</v>
+      </c>
+      <c r="D24">
+        <v>62042557176</v>
+      </c>
+      <c r="E24">
+        <v>336</v>
+      </c>
+      <c r="F24">
+        <v>62042557176</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>o_los_h</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>6.2</v>
+      </c>
+      <c r="C25">
+        <v>1.2258</v>
+      </c>
+      <c r="D25">
+        <v>62042557176</v>
+      </c>
+      <c r="E25">
+        <v>5.0582</v>
+      </c>
+      <c r="F25">
+        <v>62042557176</v>
+      </c>
+      <c r="G25">
         <v>0</v>
       </c>
     </row>
